--- a/assets/constructions/examples/ctd_mha3.xlsx
+++ b/assets/constructions/examples/ctd_mha3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,47 +574,76 @@
           <t>dcsfms</t>
         </is>
       </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>316-16UM400-16040G  1030</t>
+          <t>80451607DL16 WP15PE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CoroMill® 316..UM..G</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PMKS</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>PMKN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>16</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>METRIC_EH:16</t>
+          <t>DUOLOCK:DL16</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -624,22 +653,18 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>HC</t>
-        </is>
-      </c>
+          <t>WP15PE</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PVD(Ti,Al)</t>
+          <t>AlTiN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>COROMANT</t>
+          <t>DUO-LOCK</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -652,18 +677,16 @@
         <v>15.5</v>
       </c>
       <c r="T2" t="n">
-        <v>18.7</v>
+        <v>36</v>
       </c>
       <c r="U2" t="n">
         <v>15.5</v>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>80000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063</v>
-      </c>
+      <c r="V2" t="n">
+        <v>13</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
@@ -674,56 +697,67 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>9,2</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+          <t>2018/Достижения</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>ZDL16</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>80451009DL10 WP15PE</t>
+          <t>MM HR3.0/125-6.5-2T08 IC908</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>ISCAR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>MM HR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMKN</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SH</t>
-        </is>
-      </c>
+          <t>PMKSH</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>12.7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>DUOLOCK:DL10</t>
+          <t>ISCAR_MM:T08</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -733,20 +767,16 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>WP15PE</t>
+          <t>IC908</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>AlTiN</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>DUO-LOCK</t>
-        </is>
-      </c>
+          <t>TiAlN</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
@@ -754,17 +784,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="T3" t="n">
-        <v>23</v>
-      </c>
-      <c r="U3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="V3" t="n">
-        <v>8</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
@@ -777,15 +803,22 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018/Достижения</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>ZDL10</t>
-        </is>
-      </c>
+          <t>2013/Multi_Master_Catalog.pdf</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -877,51 +910,58 @@
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>80451203DL12 WP15PE</t>
+          <t>316-20UM400-20060G  1030</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>CoroMill® 316..UM..G</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PMKN</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SH</t>
-        </is>
-      </c>
+          <t>PMKS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>DUOLOCK:DL12</t>
+          <t>METRIC_EH:20</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -931,18 +971,22 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>WP15PE</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>AlTiN</t>
+          <t>PVD(Ti,Al)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DUO-LOCK</t>
+          <t>COROMANT</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -952,19 +996,21 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>11.5</v>
+        <v>19.3</v>
       </c>
       <c r="T5" t="n">
-        <v>27</v>
+        <v>21.3</v>
       </c>
       <c r="U5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+        <v>19.3</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.12</v>
+      </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
@@ -975,20 +1021,27 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018/Достижения</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>ZDL12</t>
-        </is>
-      </c>
+          <t>9,2</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>PMKS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>316-20UM400-20060G  1030</t>
+          <t>A316-20UM400-07563G 1030</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1008,23 +1061,23 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>6.35</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>6.35</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>METRIC_EH:20</t>
+          <t>INCH_EH:20</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1059,20 +1112,20 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>19.3</v>
+        <v>18.5</v>
       </c>
       <c r="T6" t="n">
         <v>21.3</v>
       </c>
       <c r="U6" t="n">
-        <v>19.3</v>
+        <v>18.5</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
         <v>80000</v>
       </c>
       <c r="X6" t="n">
-        <v>0.12</v>
+        <v>0.107</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1084,11 +1137,22 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9,2</t>
+          <t>10,2</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>PMKS</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
